--- a/artfynd/A 51489-2025 artfynd.xlsx
+++ b/artfynd/A 51489-2025 artfynd.xlsx
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82245885</v>
+        <v>82245859</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -786,27 +786,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82246095</v>
+        <v>82245906</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221343</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -817,7 +817,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredåker, Hls</t>
+          <t>Bredåker Forstäkten, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>BWA198707250742</t>
+          <t>BWA198707250827</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gammal granskog m. kant mot väg</t>
+          <t>Gammal vall+ kanter</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -897,27 +897,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82245906</v>
+        <v>82246095</v>
       </c>
       <c r="B4" t="n">
-        <v>101972</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221343</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,7 +928,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredåker Forstäkten, Hls</t>
+          <t>Bredåker, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>BWA198707250827</t>
+          <t>BWA198707250742</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Gammal vall+ kanter</t>
+          <t>Gammal granskog m. kant mot väg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1008,27 +1008,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82245859</v>
+        <v>82245885</v>
       </c>
       <c r="B5" t="n">
-        <v>109254</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220204</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>82263785</v>
+        <v>82263784</v>
       </c>
       <c r="B6" t="n">
-        <v>104127</v>
+        <v>104628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1983-05-29</t>
+          <t>1985-05-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1983-05-29</t>
+          <t>1985-05-27</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 51489-2025 artfynd.xlsx
+++ b/artfynd/A 51489-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82245859</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82245906</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82246095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82245885</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,8 +1252,20 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82263784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>